--- a/data/trans_orig/P70C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023</t>
+          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109193</t>
+          <t>109308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>142440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>97350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195561</t>
+          <t>197304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233503</t>
+          <t>232664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>44122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>58214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>40850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>33442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61709</t>
+          <t>61967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>493</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2386</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75297</t>
+          <t>76620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>61118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121681</t>
+          <t>120576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165710</t>
+          <t>167251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42210</t>
+          <t>44200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>33054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65467</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33716</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70592</t>
+          <t>69048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58799</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96536</t>
+          <t>97269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71750</t>
+          <t>72762</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>52699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75352</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116473</t>
+          <t>115478</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>31949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26138</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51967</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>45676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>91862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35083</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50702</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45223</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23615</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37900</t>
+          <t>37911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>32307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40630</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64583</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48671</t>
+          <t>48036</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>79783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82084</t>
+          <t>99002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205949</t>
+          <t>208685</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157692</t>
+          <t>152923</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307985</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23561</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>40070</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41652</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70652</t>
+          <t>69533</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>41899</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47966</t>
+          <t>46589</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78801</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>32637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47181</t>
+          <t>46304</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71515</t>
+          <t>69296</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>56084</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>74858</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>64084</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>77741</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>124616</t>
+          <t>124314</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146363</t>
+          <t>147115</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>35411</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>57105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>324</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>56926</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>63762</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>91991</t>
+          <t>90397</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>31548</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45970</t>
+          <t>45673</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>80372</t>
+          <t>82785</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>118052</t>
+          <t>120193</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>70522</t>
+          <t>71634</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>99625</t>
+          <t>99352</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>163992</t>
+          <t>162429</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>210398</t>
+          <t>209688</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>81384</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>122743</t>
+          <t>125374</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>69199</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>133701</t>
+          <t>135700</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>181614</t>
+          <t>186400</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>39631</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>41592</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>72231</t>
+          <t>70089</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>64024</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>88693</t>
+          <t>85755</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>126455</t>
+          <t>125850</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>50643</t>
+          <t>50350</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51730</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>75559</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>84056</t>
+          <t>82244</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>116656</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>37801</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>58834</t>
+          <t>58634</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>104364</t>
+          <t>105511</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>508605</t>
+          <t>515576</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>127629</t>
+          <t>127372</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>630927</t>
+          <t>638403</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>107051</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>58282</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>154291</t>
+          <t>154502</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>127537</t>
+          <t>126373</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>42609</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>65539</t>
+          <t>65797</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>61086</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>181987</t>
+          <t>183697</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>174143</t>
+          <t>171206</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>50288</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>75043</t>
+          <t>74614</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>76709</t>
+          <t>82834</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>230682</t>
+          <t>232025</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>108715</t>
+          <t>105301</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>45655</t>
+          <t>46651</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>69767</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>57108</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>169704</t>
+          <t>167008</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>40469</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>42405</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>71967</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>618260</t>
+          <t>620219</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1204874</t>
+          <t>1241591</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>403588</t>
+          <t>408642</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>632967</t>
+          <t>622073</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1071068</t>
+          <t>1063850</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1855513</t>
+          <t>1751154</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>219954</t>
+          <t>209064</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>393699</t>
+          <t>392900</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>207446</t>
+          <t>208720</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>278603</t>
+          <t>279100</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>439866</t>
+          <t>460512</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>654186</t>
+          <t>646695</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>127748</t>
+          <t>128208</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>234791</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>127096</t>
+          <t>130309</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>179826</t>
+          <t>179165</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>267564</t>
+          <t>274116</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>392314</t>
+          <t>397369</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>204648</t>
+          <t>189660</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>357687</t>
+          <t>358699</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>179837</t>
+          <t>181263</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>244441</t>
+          <t>244680</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>406047</t>
+          <t>400394</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>581424</t>
+          <t>583656</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>149249</t>
+          <t>148517</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>285778</t>
+          <t>281497</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>189651</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>253817</t>
+          <t>253211</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>356553</t>
+          <t>364324</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>522052</t>
+          <t>526895</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>128038</t>
+          <t>129591</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111265</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>161090</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>179447</t>
+          <t>186803</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>277253</t>
+          <t>277502</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>133036</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109308</t>
+          <t>117977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142440</t>
+          <t>146897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88462</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77972</t>
+          <t>81464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97350</t>
+          <t>101415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>216306</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197304</t>
+          <t>207720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232664</t>
+          <t>240566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12707</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58214</t>
+          <t>45414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>36475</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40850</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>35618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>48294</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61967</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>487</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95418</t>
+          <t>98896</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115261</t>
+          <t>119592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>54023</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>43537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61118</t>
+          <t>66713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>144336</t>
+          <t>152919</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120576</t>
+          <t>129239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167251</t>
+          <t>174415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44200</t>
+          <t>42924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>45710</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>61008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>30737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>67971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37447</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>77512</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97269</t>
+          <t>97718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37357</t>
+          <t>39135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72762</t>
+          <t>73976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40348</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>55054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>93424</t>
+          <t>98212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75710</t>
+          <t>80207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115478</t>
+          <t>121047</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>53398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41666</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>30414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>53427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45676</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>77947</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>63538</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91862</t>
+          <t>92174</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50300</t>
+          <t>48272</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>43546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>24276</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52347</t>
+          <t>53558</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65129</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26821</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>147713</t>
+          <t>148623</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>147713</t>
+          <t>148623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147713</t>
+          <t>148623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119668</t>
+          <t>121812</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119668</t>
+          <t>121812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119668</t>
+          <t>121812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>267381</t>
+          <t>270435</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>267381</t>
+          <t>270435</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>267381</t>
+          <t>270435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>64350</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48036</t>
+          <t>61590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79783</t>
+          <t>102465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>151560</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99002</t>
+          <t>44361</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208685</t>
+          <t>70926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>215909</t>
+          <t>138541</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152923</t>
+          <t>116468</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>163561</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>29865</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>46709</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>53013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>55734</t>
+          <t>66808</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>49979</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>43380</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>55584</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>41875</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>166359</t>
+          <t>208796</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>166359</t>
+          <t>208796</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>166359</t>
+          <t>208796</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>180344</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>424379</t>
+          <t>389141</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>424379</t>
+          <t>389141</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>424379</t>
+          <t>389141</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25134</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>74858</t>
+          <t>87182</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>70830</t>
+          <t>78006</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>64099</t>
+          <t>69633</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>135857</t>
+          <t>155426</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>141487</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>147115</t>
+          <t>167755</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>46884</t>
+          <t>52509</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>37395</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>57105</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>475</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>45024</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35417</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>54991</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>77188</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>65110</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>90896</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>49227</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -5152,17 +5152,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>23878</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>33298</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>34784</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45673</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>100685</t>
+          <t>124442</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>82785</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>120193</t>
+          <t>142656</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>84605</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>85589</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>116492</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>185289</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>162429</t>
+          <t>198647</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>209688</t>
+          <t>250927</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>99728</t>
+          <t>108115</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>80510</t>
+          <t>88802</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>125374</t>
+          <t>129901</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>70511</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45573</t>
+          <t>59206</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>85483</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>156371</t>
+          <t>178625</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>135700</t>
+          <t>154783</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>186400</t>
+          <t>204274</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>26589</t>
+          <t>28739</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>57200</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>37167</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>39373</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>70089</t>
+          <t>77745</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>50869</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>64024</t>
+          <t>70495</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>104866</t>
+          <t>117276</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>98374</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>139472</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>43486</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>50350</t>
+          <t>60412</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>73363</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>60191</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>87578</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>116849</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>82244</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>138625</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>44905</t>
+          <t>55024</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>35115</t>
+          <t>43331</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>58634</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>306725</t>
+          <t>361882</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>306725</t>
+          <t>361882</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>306725</t>
+          <t>361882</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>641026</t>
+          <t>749396</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>641026</t>
+          <t>749396</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>641026</t>
+          <t>749396</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>313031</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>105511</t>
+          <t>64358</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>515576</t>
+          <t>100304</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>29241</t>
+          <t>33599</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>342272</t>
+          <t>115211</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>127372</t>
+          <t>96591</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>638403</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>55908</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>57534</t>
+          <t>69431</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>106462</t>
+          <t>127923</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>107430</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>154502</t>
+          <t>149505</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>89326</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>126373</t>
+          <t>111419</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>52479</t>
+          <t>60979</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>41538</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>65797</t>
+          <t>74762</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>125966</t>
+          <t>150305</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>61086</t>
+          <t>128387</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>183697</t>
+          <t>173036</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>100554</t>
+          <t>118798</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>34142</t>
+          <t>100955</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>171206</t>
+          <t>142579</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>72896</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>74614</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>162959</t>
+          <t>191694</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>82834</t>
+          <t>166295</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>232025</t>
+          <t>217153</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>60381</t>
+          <t>68349</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>105301</t>
+          <t>87215</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>66406</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>53984</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>80975</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>117201</t>
+          <t>134755</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>115666</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>167008</t>
+          <t>156551</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>39115</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>33235</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>48192</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>64438</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>797666</t>
+          <t>616559</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>620219</t>
+          <t>569631</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1241591</t>
+          <t>665218</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>478557</t>
+          <t>413798</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>408642</t>
+          <t>382251</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>622073</t>
+          <t>446128</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>1276223</t>
+          <t>1030356</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1063850</t>
+          <t>974186</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1751154</t>
+          <t>1084283</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -7198,32 +7198,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>365771</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>209064</t>
+          <t>327980</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>392900</t>
+          <t>407489</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>250568</t>
+          <t>283200</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>208720</t>
+          <t>257127</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>279100</t>
+          <t>309662</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>580786</t>
+          <t>648971</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>460512</t>
+          <t>599128</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>646695</t>
+          <t>691590</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>224870</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>128208</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>232060</t>
+          <t>252073</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>153950</t>
+          <t>175524</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>130309</t>
+          <t>152823</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>179165</t>
+          <t>198989</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>400395</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>274116</t>
+          <t>364678</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>397369</t>
+          <t>441219</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>338816</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>189660</t>
+          <t>302745</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>358699</t>
+          <t>378338</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>242881</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>181263</t>
+          <t>218355</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>268780</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>581697</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>400394</t>
+          <t>535008</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>583656</t>
+          <t>629366</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>264940</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>148517</t>
+          <t>234243</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>281497</t>
+          <t>304435</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>226395</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>189651</t>
+          <t>227281</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>253211</t>
+          <t>279162</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>465212</t>
+          <t>517910</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>364324</t>
+          <t>474301</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>526895</t>
+          <t>560037</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>120028</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>63454</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>129591</t>
+          <t>146686</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>135805</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>111265</t>
+          <t>125897</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>161090</t>
+          <t>166887</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>265342</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>277502</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
